--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104616_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104616_W18.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1553</v>
+        <v>3.7915</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3969</v>
+        <v>4.9991</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2417</v>
+        <v>-1.2076</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9418</v>
+        <v>1.9517</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2726</v>
+        <v>1.2751</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9802</v>
+        <v>2.9683</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2339</v>
+        <v>2.2236</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0384</v>
+        <v>-1.0166</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5081</v>
+        <v>0.1277</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8438</v>
+        <v>0.4665</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3357</v>
+        <v>-0.3388</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.909</v>
+        <v>-1.9009</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3252</v>
+        <v>2.1509</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8737</v>
+        <v>1.4391</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5485</v>
+        <v>0.7118</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0451</v>
+        <v>-0.6807</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7546</v>
+        <v>0.9937</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7997</v>
+        <v>-1.6743</v>
       </c>
       <c r="J3" t="n">
-        <v>1.886</v>
+        <v>0.1639</v>
       </c>
       <c r="K3" t="n">
-        <v>2.078</v>
+        <v>0.8791</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.192</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9311</v>
+        <v>-0.8446</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3234</v>
+        <v>0.1146</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6077</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.722</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7064</v>
+        <v>0.1487</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7512</v>
+        <v>0.1857</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0448</v>
+        <v>-0.037</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4371</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7317</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2946</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7864</v>
+        <v>1.9691</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2127</v>
+        <v>3.2267</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5737</v>
+        <v>-1.2577</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6812</v>
+        <v>-0.0392</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9927</v>
+        <v>0.7608</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.674</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1714</v>
+        <v>1.8669</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8832</v>
+        <v>2.0684</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7117</v>
+        <v>-0.2015</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8526</v>
+        <v>-1.9061</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1096</v>
+        <v>-1.3077</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.5984</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2129</v>
+        <v>1.3448</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0514</v>
+        <v>1.1401</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1615</v>
+        <v>0.2047</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>0.4358</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>2.7237</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7157</v>
+        <v>0.7862</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0106</v>
+        <v>1.0065</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2949</v>
+        <v>-0.2204</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3211</v>
+        <v>-0.3171</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0361</v>
+        <v>0.0373</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3572</v>
+        <v>-0.3544</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1266</v>
+        <v>0.1262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4477</v>
+        <v>-0.4433</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0974</v>
+        <v>-0.0349</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1113</v>
+        <v>0.1743</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6552</v>
+        <v>0.486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7531</v>
+        <v>0.7147</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0979</v>
+        <v>-0.2287</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0458</v>
+        <v>0.0596</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0102</v>
+        <v>-0.0033</v>
       </c>
       <c r="I6" t="n">
-        <v>0.056</v>
+        <v>0.0629</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5565</v>
+        <v>0.5431</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5107</v>
+        <v>-0.4835</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2979</v>
+        <v>-0.4841</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1966</v>
+        <v>0.1716</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4945</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9472</v>
+        <v>-0.3371</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3721</v>
+        <v>-1.6364</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4249</v>
+        <v>1.2993</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6089</v>
+        <v>0.5837</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6464</v>
+        <v>0.649</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0375</v>
+        <v>-0.0653</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3169</v>
+        <v>1.27</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9626</v>
+        <v>0.9513</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3542</v>
+        <v>0.3187</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.708</v>
+        <v>-0.6863</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4733</v>
+        <v>0.1685</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3811</v>
+        <v>0.4202</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.2516</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0515</v>
+        <v>0.0488</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.27</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. OBASOHAN</t>
+          <t>G. FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5714</v>
+        <v>-1.2806</v>
       </c>
       <c r="E8" t="n">
-        <v>0.187</v>
+        <v>-0.2311</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7585</v>
+        <v>-1.0496</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0076</v>
+        <v>-1.4218</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6956</v>
+        <v>-0.2213</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7033</v>
+        <v>-1.2006</v>
       </c>
       <c r="J8" t="n">
-        <v>1.113</v>
+        <v>0.1122</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0913</v>
+        <v>0.8274</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9784</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1206</v>
+        <v>-1.534</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3957</v>
+        <v>-1.0487</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7249</v>
+        <v>-0.4854</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2655</v>
+        <v>0.0242</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1966</v>
+        <v>-0.1141</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0689</v>
+        <v>0.1383</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2122</v>
+        <v>-1.4764</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5068</v>
+        <v>-0.2292</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2946</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ</t>
+          <t>R. OBASOHAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8102</v>
+        <v>-1.4469</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6438</v>
+        <v>0.5188</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1664</v>
+        <v>-1.9657</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4258</v>
+        <v>-0.0162</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2237</v>
+        <v>1.6864</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2021</v>
+        <v>-1.7026</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1195</v>
+        <v>1.0698</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8312</v>
+        <v>2.0609</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7117</v>
+        <v>-0.9912</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5453</v>
+        <v>-1.086</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0549</v>
+        <v>-0.3745</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4904</v>
+        <v>-0.7114</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5878</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4939</v>
+        <v>0.4114</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5383</v>
+        <v>0.5966</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0445</v>
+        <v>-0.1852</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4783</v>
+        <v>0.2066</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2249</v>
+        <v>2.4945</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6009</v>
+        <v>-2.3994</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5894</v>
+        <v>-0.3107</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1903</v>
+        <v>-2.0888</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7784</v>
+        <v>-1.8527</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2235</v>
+        <v>-1.7642</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4451</v>
+        <v>-0.0885</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3314</v>
+        <v>0.6979</v>
       </c>
       <c r="K10" t="n">
-        <v>1.697</v>
+        <v>-0.0829</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6344</v>
+        <v>0.7809</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.553</v>
+        <v>-2.5506</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4735</v>
+        <v>-1.6813</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0795</v>
+        <v>-0.8694</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6206</v>
+        <v>0.2938</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5263</v>
+        <v>0.2481</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0944</v>
+        <v>0.0457</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1853</v>
+        <v>0.9805</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.951</v>
+        <v>-2.6294</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7315</v>
+        <v>0.5962</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2195</v>
+        <v>-3.2257</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8527</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7779</v>
+        <v>1.229</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0747</v>
+        <v>-0.4392</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7311</v>
+        <v>2.3222</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0764</v>
+        <v>1.6892</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8074</v>
+        <v>0.633</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5838</v>
+        <v>-1.5325</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7016</v>
+        <v>-0.4603</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8822</v>
+        <v>-1.0722</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2671</v>
+        <v>0.5808</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2208</v>
+        <v>0.5503</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0463</v>
+        <v>0.0305</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9834000000000001</v>
+        <v>-2.1789</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.27</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7741</v>
+        <v>-4.3617</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6218</v>
+        <v>-4.2327</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1523</v>
+        <v>-0.129</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2115</v>
+        <v>-4.2219</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4096</v>
+        <v>-2.4178</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8019</v>
+        <v>-1.804</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.1731</v>
+        <v>-3.2053</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4484</v>
+        <v>-1.4694</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.7247</v>
+        <v>-1.7359</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0384</v>
+        <v>-1.0166</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4718</v>
+        <v>-0.0487</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6775</v>
+        <v>-0.2535</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2056</v>
+        <v>0.2047</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.016999999999998</v>
+        <v>-3.271399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>4.654199999999998</v>
+        <v>6.090199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.6714</v>
+        <v>-9.3621</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.1701</v>
+        <v>-5.1648</v>
       </c>
       <c r="H13" t="n">
-        <v>2.200099999999999</v>
+        <v>2.2247</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.3704</v>
+        <v>-7.3893</v>
       </c>
       <c r="J13" t="n">
-        <v>8.1595</v>
+        <v>7.935200000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>9.453099999999999</v>
+        <v>9.340399999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2938</v>
+        <v>-1.4053</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.3296</v>
+        <v>-13.1001</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.252999999999999</v>
+        <v>-7.116000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.076600000000001</v>
+        <v>-5.9842</v>
       </c>
       <c r="P13" t="n">
-        <v>1.134</v>
+        <v>1.138</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7441</v>
+        <v>-14.7959</v>
       </c>
       <c r="R13" t="n">
-        <v>15.8783</v>
+        <v>15.9342</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7863000000000002</v>
+        <v>2.5322</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4367</v>
+        <v>3.2024</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6504</v>
+        <v>-0.6700999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.767199999999999</v>
+        <v>-1.7769</v>
       </c>
       <c r="W13" t="n">
-        <v>9.802299999999999</v>
+        <v>9.748800000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.5696</v>
+        <v>-11.5257</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.2828</v>
+        <v>8.1937</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9406</v>
+        <v>4.9403</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3421</v>
+        <v>3.2535</v>
       </c>
       <c r="G14" t="n">
-        <v>5.204</v>
+        <v>5.177</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8599</v>
+        <v>-0.867</v>
       </c>
       <c r="I14" t="n">
-        <v>6.0639</v>
+        <v>6.044</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4561</v>
+        <v>5.404</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0559</v>
+        <v>-0.0764</v>
       </c>
       <c r="L14" t="n">
-        <v>5.5121</v>
+        <v>5.4804</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2521</v>
+        <v>-0.227</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1047</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8861</v>
+        <v>0.1784</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7815</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4102</v>
+        <v>2.4082</v>
       </c>
       <c r="W14" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2654</v>
+        <v>4.806</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8703</v>
+        <v>4.9469</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6049</v>
+        <v>-0.1409</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1655</v>
+        <v>5.1577</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5715</v>
+        <v>3.5592</v>
       </c>
       <c r="I15" t="n">
-        <v>1.594</v>
+        <v>1.5986</v>
       </c>
       <c r="J15" t="n">
-        <v>5.354</v>
+        <v>5.3269</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3119</v>
+        <v>4.292</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0422</v>
+        <v>1.035</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1885</v>
+        <v>-0.1692</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5391</v>
+        <v>-0.986</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6956</v>
+        <v>-0.5786</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8435</v>
+        <v>-0.4074</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2478</v>
+        <v>2.0877</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6652</v>
+        <v>1.3787</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5826</v>
+        <v>0.709</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0394</v>
+        <v>1.5799</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1861</v>
+        <v>1.1716</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1467</v>
+        <v>0.4083</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1654</v>
+        <v>2.4242</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.603</v>
+        <v>1.9478</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5625</v>
+        <v>0.4764</v>
       </c>
       <c r="M16" t="n">
-        <v>0.126</v>
+        <v>-0.8442</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5831</v>
+        <v>-0.7761</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7091</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8335</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.738</v>
+        <v>0.369</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0956</v>
+        <v>0.3452</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0271</v>
+        <v>1.6749</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2847</v>
+        <v>-0.0586</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7423999999999999</v>
+        <v>1.7335</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5739</v>
+        <v>-1.0336</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1687</v>
+        <v>-1.1889</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4052</v>
+        <v>0.1553</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4392</v>
+        <v>-1.1802</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9568</v>
+        <v>-0.614</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4824</v>
+        <v>-0.5662</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8653</v>
+        <v>0.1467</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.788</v>
+        <v>-0.5749</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0772</v>
+        <v>0.7215</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6554</v>
+        <v>0.2532</v>
       </c>
       <c r="T17" t="n">
-        <v>0.248</v>
+        <v>0.0322</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4074</v>
+        <v>0.2211</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9320000000000001</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1342</v>
+        <v>0.9357</v>
       </c>
       <c r="E18" t="n">
-        <v>2.471</v>
+        <v>0.3912</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6052</v>
+        <v>0.5445</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8063</v>
+        <v>-0.6193</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.5527</v>
+        <v>-1.7172</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7463</v>
+        <v>1.0978</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1411</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4342</v>
+        <v>-0.6108</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2931</v>
+        <v>1.4369</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6653</v>
+        <v>-1.4455</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4532</v>
+        <v>-0.3391</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7914</v>
+        <v>-0.0384</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7462</v>
+        <v>-0.5927</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9548</v>
+        <v>0.5543</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3461</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1567</v>
+        <v>0.8498</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1646</v>
+        <v>1.4935</v>
       </c>
       <c r="F19" t="n">
-        <v>0.008</v>
+        <v>-0.6437</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6131</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7112</v>
+        <v>0.1472</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0982</v>
+        <v>-1.0812</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8572</v>
+        <v>-0.1623</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5928</v>
+        <v>1.2681</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4499</v>
+        <v>-1.4303</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4702</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1185</v>
+        <v>-1.1209</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3517</v>
+        <v>0.3492</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1314</v>
+        <v>-0.2358</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1825</v>
+        <v>-0.1769</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0511</v>
+        <v>-0.0589</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>3.4262</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3145</v>
+        <v>-1.2204</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8361</v>
+        <v>-0.9724</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1505</v>
+        <v>-0.248</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9271</v>
+        <v>-1.1854</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1604</v>
+        <v>0.3131</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0875</v>
+        <v>-1.4985</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1287</v>
+        <v>0.0036</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2948</v>
+        <v>1.4339</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7984</v>
+        <v>-1.189</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O20" t="n">
-        <v>0.336</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.5878</v>
+        <v>-2.7316</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4139</v>
+        <v>0.3112</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8861</v>
+        <v>0.5084</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5278</v>
+        <v>-0.1972</v>
       </c>
       <c r="V20" t="n">
-        <v>1.7997</v>
+        <v>1.2472</v>
       </c>
       <c r="W20" t="n">
-        <v>3.4387</v>
+        <v>1.2472</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2705</v>
+        <v>-1.2352</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1992</v>
+        <v>0.8036</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4697</v>
+        <v>-2.0389</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4519</v>
+        <v>-1.8031</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4199</v>
+        <v>-2.5478</v>
       </c>
       <c r="I21" t="n">
-        <v>0.032</v>
+        <v>0.7447</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4695</v>
+        <v>-1.1588</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9871</v>
+        <v>-1.4414</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4824</v>
+        <v>0.2826</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0176</v>
+        <v>-0.6442</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5672</v>
+        <v>-1.1064</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4504</v>
+        <v>0.4622</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>0.238</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0907</v>
+        <v>1.1006</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1473</v>
+        <v>-0.4237</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.9604</v>
+        <v>-1.2472</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9604</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3925</v>
+        <v>-1.3559</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0574</v>
+        <v>-0.1696</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3351</v>
+        <v>-1.1863</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1876</v>
+        <v>0.458</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3131</v>
+        <v>0.4221</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5007</v>
+        <v>0.0359</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0241</v>
+        <v>1.4589</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4475</v>
+        <v>0.9825</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4234</v>
+        <v>0.4764</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2116</v>
+        <v>-1.0009</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1344</v>
+        <v>-0.5604</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0772</v>
+        <v>-0.4405</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.722</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1294</v>
+        <v>0.1359</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3871</v>
+        <v>-0.2627</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2577</v>
+        <v>0.3986</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2534</v>
+        <v>-1.9497</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5458</v>
+        <v>-1.9814</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3654</v>
+        <v>-0.8403</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1804</v>
+        <v>-1.1411</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0385</v>
+        <v>-0.0337</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1371</v>
+        <v>-0.1351</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="J23" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="K23" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0854</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O23" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4927</v>
+        <v>0.0523</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7168</v>
+        <v>0.2462</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2241</v>
+        <v>-0.1939</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0068</v>
+        <v>-2.0262</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.8951</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1202</v>
+        <v>-1.131</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8085</v>
+        <v>-0.799</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4301</v>
+        <v>-0.4253</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3785</v>
+        <v>-0.3737</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7527</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L24" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5612</v>
+        <v>-1.5485</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0708</v>
+        <v>-1.0631</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4231</v>
+        <v>-0.4564</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1449</v>
+        <v>-0.1775</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9851</v>
+        <v>-3.3458</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1217</v>
+        <v>-1.6563</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8633</v>
+        <v>-1.6894</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8047</v>
+        <v>-0.7998</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9567</v>
+        <v>-0.9564</v>
       </c>
       <c r="I25" t="n">
-        <v>0.152</v>
+        <v>0.1566</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6398</v>
+        <v>-0.6435</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L25" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1649</v>
+        <v>-0.1563</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O25" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3478</v>
+        <v>0.1253</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0333</v>
+        <v>0.1906</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5.017</v>
+        <v>7.382899999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>9.6714</v>
+        <v>9.3619</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.654199999999999</v>
+        <v>-1.978800000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>5.170099999999998</v>
+        <v>5.1647</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.2002</v>
+        <v>-2.2245</v>
       </c>
       <c r="I26" t="n">
-        <v>7.370200000000001</v>
+        <v>7.389199999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>13.3298</v>
+        <v>13.1001</v>
       </c>
       <c r="K26" t="n">
-        <v>7.2532</v>
+        <v>7.116000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>6.0768</v>
+        <v>5.9843</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.1595</v>
+        <v>-7.935199999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-9.4533</v>
+        <v>-9.3405</v>
       </c>
       <c r="O26" t="n">
-        <v>1.2938</v>
+        <v>1.4052</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.8783</v>
+        <v>-15.9342</v>
       </c>
       <c r="R26" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7862999999999996</v>
+        <v>1.5792</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6504999999999997</v>
+        <v>0.6703999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.4366</v>
+        <v>0.9090000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>1.767500000000001</v>
+        <v>1.7773</v>
       </c>
       <c r="W26" t="n">
-        <v>11.5696</v>
+        <v>11.5259</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.802199999999999</v>
+        <v>-9.748700000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104616_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104616_W18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.9009</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-11.5257</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104616_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-9.748700000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
